--- a/data/fmsForecastOutput/File1/RPT_RPT7370303776679ST_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT7370303776679ST_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>525.7446861388846</v>
+        <v>371.1012020151579</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>561.526874778127</v>
+        <v>403.4648127046563</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>602.4522700238122</v>
+        <v>433.2437460736331</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>637.3706521017881</v>
+        <v>461.6050719669364</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>678.7571483337661</v>
+        <v>490.0822807975661</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>45.31472537891992</v>
+        <v>31.98577085125618</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>51.17606325963209</v>
+        <v>36.77070805590122</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>57.9488065532683</v>
+        <v>41.67294121182734</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>65.39044139334983</v>
+        <v>47.35793734115406</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>75.03547156255473</v>
+        <v>54.17777939336712</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>54216767.67339604</v>
+        <v>38269350.47263379</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>62179819.38206437</v>
+        <v>44677058.76215915</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>71375912.696826</v>
+        <v>51328826.09102832</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>81552007.84241624</v>
+        <v>59062682.48311946</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>95046278.11887069</v>
+        <v>68626160.14603041</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>534.6164055963731</v>
+        <v>377.3633780131583</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>571.0024035513379</v>
+        <v>410.2731109597874</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>612.6183975512835</v>
+        <v>440.5545512481076</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>648.126012574209</v>
+        <v>469.394462533525</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>690.2108884447811</v>
+        <v>498.3522122318773</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>55.18193508190548</v>
+        <v>38.95062181000892</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>62.25301197410799</v>
+        <v>44.72964865013542</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>70.41489977251828</v>
+        <v>50.63772928540786</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>79.34775647935197</v>
+        <v>57.46629017085152</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>90.89573510808297</v>
+        <v>65.62934811941879</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>54216767.67339604</v>
+        <v>38269350.47263379</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>62179819.38206437</v>
+        <v>44677058.76215915</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>71375912.696826</v>
+        <v>51328826.09102832</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>81552007.84241624</v>
+        <v>59062682.48311946</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>95046278.11887069</v>
+        <v>68626160.14603041</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>1562.899820031829</v>
+        <v>1103.184243631821</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>1676.470624165207</v>
+        <v>1204.566558373179</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>1807.173200207154</v>
+        <v>1299.598635628595</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>1906.501875589519</v>
+        <v>1380.752619138784</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>2020.325454925211</v>
+        <v>1458.733822591812</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>102.0875524931386</v>
+        <v>72.05924393738388</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>111.3783079577132</v>
+        <v>80.026803428695</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>124.2656707214718</v>
+        <v>89.36359619907205</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>139.4255160233663</v>
+        <v>100.9766362619034</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>159.3176458849554</v>
+        <v>115.0319806254646</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>27075095.88191539</v>
+        <v>19111154.01570753</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>29709194.45279993</v>
+        <v>21346453.4350959</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>33317745.29128301</v>
+        <v>23959903.96372026</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>37537461.76319435</v>
+        <v>27185889.14544129</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>43164315.19002604</v>
+        <v>31165892.7739617</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>1587.472936028264</v>
+        <v>1120.529356886522</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>1702.829387909507</v>
+        <v>1223.505682547963</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>1835.586970626191</v>
+        <v>1320.031927393552</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>1936.477368027242</v>
+        <v>1402.461876403775</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>2052.090569437423</v>
+        <v>1481.669160462503</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>102.5208428423861</v>
+        <v>72.36508509244767</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>111.8525414715252</v>
+        <v>80.36754654901192</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>124.7982869665548</v>
+        <v>89.74661833847966</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>140.0305064646682</v>
+        <v>101.4147906361934</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>160.0200305371808</v>
+        <v>115.5391228020742</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>27075095.88191539</v>
+        <v>19111154.01570753</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>29709194.45279993</v>
+        <v>21346453.4350959</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>33317745.29128301</v>
+        <v>23959903.96372026</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>37537461.76319435</v>
+        <v>27185889.14544129</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>43164315.19002604</v>
+        <v>31165892.7739617</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>674.9159616585608</v>
+        <v>476.3947666281775</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>715.3415380202606</v>
+        <v>513.9826709377984</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>764.6783632314756</v>
+        <v>549.9059252909137</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>806.6213887443846</v>
+        <v>584.1821519118731</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>856.3504122896214</v>
+        <v>618.3098098006792</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>55.61598365125634</v>
+        <v>39.2569816947679</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>62.01347043660075</v>
+        <v>44.55752598589276</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>69.80399040697856</v>
+        <v>50.19839684169003</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>78.5351468841972</v>
+        <v>56.87777654760925</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>89.88622615390634</v>
+        <v>64.90045967085504</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>81291863.55531144</v>
+        <v>57380504.48834132</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>91889013.83486429</v>
+        <v>66023512.19725505</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>104693657.988109</v>
+        <v>75288730.05474858</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>119089469.6056106</v>
+        <v>86248571.62856075</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>138210593.3088967</v>
+        <v>99792052.91999209</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>686.1929673934951</v>
+        <v>484.3547302689197</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>727.2988452767468</v>
+        <v>522.5741596103583</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>777.4632690249665</v>
+        <v>559.0999809725947</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>820.1087615789902</v>
+        <v>593.9501578141495</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>870.6702648551141</v>
+        <v>628.6491582602314</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>65.21071091640428</v>
+        <v>46.02949577949711</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>72.67201567386977</v>
+        <v>52.21583639874022</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>81.7522806207248</v>
+        <v>58.79081412661007</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>91.90094707754967</v>
+        <v>66.55773548240896</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>105.0706821249326</v>
+        <v>75.86407684045447</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>81291863.55531144</v>
+        <v>57380504.48834132</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>91889013.83486429</v>
+        <v>66023512.19725505</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>104693657.988109</v>
+        <v>75288730.05474858</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>119089469.6056106</v>
+        <v>86248571.62856075</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>138210593.3088967</v>
+        <v>99792052.91999209</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>1523.353343487997</v>
+        <v>1075.270130818456</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>1638.022615832569</v>
+        <v>1176.941006045047</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>1779.022631339218</v>
+        <v>1279.35439131355</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>1907.795609550437</v>
+        <v>1381.689176741368</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>2065.714141544101</v>
+        <v>1491.505341774555</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>163.1362207564806</v>
+        <v>115.1508979738104</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>182.2754307563675</v>
+        <v>130.9673180199982</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>206.3389190163734</v>
+        <v>148.3851849280682</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>233.6586133263297</v>
+        <v>169.2233567732462</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>268.3575864237905</v>
+        <v>193.7619371466482</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>10322723.77456123</v>
+        <v>7286370.290204898</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>11683955.76268346</v>
+        <v>8395077.40430617</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>13388452.67630777</v>
+        <v>9628081.971859964</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>15335881.89967139</v>
+        <v>11106756.89286915</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>17864346.98419591</v>
+        <v>12898575.08276807</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2368,49 +2368,49 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>2005.546509294253</v>
+        <v>1415.629713637951</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>2156.512507995119</v>
+        <v>1549.482880258311</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>2342.143825980947</v>
+        <v>1684.313586612994</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>2511.677833338427</v>
+        <v>1819.04081360303</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>2719.582953937429</v>
+        <v>1963.617531399904</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>187.5477154644201</v>
+        <v>132.3819305640421</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>209.6755471537543</v>
+        <v>150.6546655857707</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>237.5151288469842</v>
+        <v>170.8050351585734</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>269.2110311768674</v>
+        <v>194.9716029193047</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>309.5170540853674</v>
+        <v>223.4802629533113</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>10322723.77456123</v>
+        <v>7286370.290204898</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>11683955.76268346</v>
+        <v>8395077.40430617</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>13388452.67630777</v>
+        <v>9628081.971859964</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>15335881.89967139</v>
+        <v>11106756.89286915</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>17864346.98419591</v>
+        <v>12898575.08276807</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>720.1062821332695</v>
+        <v>508.292665296682</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>763.8817096615487</v>
+        <v>548.8594145396374</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>817.529407225964</v>
+        <v>587.9128566470629</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>863.4810932088706</v>
+        <v>625.3618425397227</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>917.8561006809263</v>
+        <v>662.7186927488826</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>60.07748730677054</v>
+        <v>42.40616545799629</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>67.00024842916092</v>
+        <v>48.1405912220791</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>75.46585380382247</v>
+        <v>54.27003028510241</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>84.97080577919776</v>
+        <v>61.53869503580481</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>97.29228259062057</v>
+        <v>70.24784635105365</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>91614587.32987265</v>
+        <v>64666874.77854621</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>103572969.5975477</v>
+        <v>74418589.6015612</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>118082110.6644168</v>
+        <v>84916812.02660853</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>134425351.505282</v>
+        <v>97355328.5214299</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>156074940.2930926</v>
+        <v>112690628.0027602</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>741.1282678646639</v>
+        <v>523.1311987498061</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>786.0679014429301</v>
+        <v>564.8004955708726</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>841.1790250669897</v>
+        <v>604.9200912011171</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>888.3654199818208</v>
+        <v>643.3839029687034</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>944.1392633050407</v>
+        <v>681.6958975227434</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>70.38378063768333</v>
+        <v>49.68094341296706</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>78.45494342033204</v>
+        <v>56.37094561735567</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>88.31940133143598</v>
+        <v>63.51344804869044</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>99.36735825303634</v>
+        <v>71.9651590916677</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>113.664232278344</v>
+        <v>82.06886828112448</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>91614587.32987265</v>
+        <v>64666874.77854621</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>103572969.5975477</v>
+        <v>74418589.6015612</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>118082110.6644168</v>
+        <v>84916812.02660853</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>134425351.505282</v>
+        <v>97355328.5214299</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>156074940.2930926</v>
+        <v>112690628.0027602</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>720.1062821332696</v>
+        <v>508.292665296682</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>763.8817096615488</v>
+        <v>548.8594145396376</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>817.529407225964</v>
+        <v>587.912856647063</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>863.4810932088706</v>
+        <v>625.3618425397227</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>917.8561006809263</v>
+        <v>662.7186927488825</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>60.07748730677056</v>
+        <v>42.40616545799629</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>67.00024842916093</v>
+        <v>48.14059122207911</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>75.46585380382247</v>
+        <v>54.27003028510241</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>84.97080577919776</v>
+        <v>61.53869503580481</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>97.29228259062057</v>
+        <v>70.24784635105365</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>91614587.32987267</v>
+        <v>64666874.77854621</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>103572969.5975478</v>
+        <v>74418589.60156122</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>118082110.6644168</v>
+        <v>84916812.02660854</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>134425351.505282</v>
+        <v>97355328.5214299</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>156074940.2930926</v>
+        <v>112690628.0027602</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>741.1282678646641</v>
+        <v>523.1311987498061</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>786.0679014429302</v>
+        <v>564.8004955708726</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>841.1790250669895</v>
+        <v>604.920091201117</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>888.3654199818207</v>
+        <v>643.3839029687034</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>944.1392633050407</v>
+        <v>681.6958975227434</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>70.38378063768332</v>
+        <v>49.68094341296706</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>78.45494342033204</v>
+        <v>56.37094561735567</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>88.31940133143597</v>
+        <v>63.51344804869042</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>99.36735825303634</v>
+        <v>71.9651590916677</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>113.664232278344</v>
+        <v>82.06886828112447</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>91614587.32987267</v>
+        <v>64666874.77854621</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>103572969.5975478</v>
+        <v>74418589.60156122</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>118082110.6644168</v>
+        <v>84916812.02660854</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>134425351.505282</v>
+        <v>97355328.5214299</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>156074940.2930926</v>
+        <v>112690628.0027602</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="AW16" s="176" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" thickBot="1">
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="AW17" s="177" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="18" ht="30.3" customHeight="1" thickBot="1">
@@ -3295,7 +3295,7 @@
         <v>17721.2735043261</v>
       </c>
       <c r="E20" s="80" t="n">
-        <v>18436.38744059719</v>
+        <v>18436.38744059718</v>
       </c>
       <c r="F20" s="80" t="n">
         <v>19689.18165978053</v>
@@ -3666,34 +3666,34 @@
         </is>
       </c>
       <c r="AS22" s="178" t="n">
-        <v>0.97222200886944</v>
+        <v>0.915</v>
       </c>
       <c r="AT22" s="178" t="n">
-        <v>0.949877939943838</v>
+        <v>0.91</v>
       </c>
       <c r="AU22" s="178" t="n">
-        <v>0.943844334714395</v>
+        <v>0.905</v>
       </c>
       <c r="AV22" s="178" t="n">
-        <v>0.932019789921236</v>
+        <v>0.9</v>
       </c>
       <c r="AW22" s="178" t="n">
-        <v>0.9296716375637419</v>
+        <v>0.895</v>
       </c>
       <c r="AX22" s="178" t="n">
-        <v>0.949183430955845</v>
+        <v>0.9</v>
       </c>
       <c r="AY22" s="178" t="n">
-        <v>0.9487365842958559</v>
+        <v>0.8975000000000001</v>
       </c>
       <c r="AZ22" s="178" t="n">
-        <v>0.947337586100609</v>
+        <v>0.895</v>
       </c>
       <c r="BA22" s="178" t="n">
-        <v>0.94373489701852</v>
+        <v>0.8925000000000001</v>
       </c>
       <c r="BB22" s="178" t="n">
-        <v>0.941703088585464</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="23" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -3803,34 +3803,34 @@
         </is>
       </c>
       <c r="AS23" s="178" t="n">
-        <v>0.9722</v>
+        <v>0.9349999999999999</v>
       </c>
       <c r="AT23" s="178" t="n">
-        <v>0.9499</v>
+        <v>0.9299999999999999</v>
       </c>
       <c r="AU23" s="178" t="n">
-        <v>0.9438</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="AV23" s="178" t="n">
-        <v>0.9319999999999999</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="AW23" s="178" t="n">
-        <v>0.9297</v>
+        <v>0.9149999999999999</v>
       </c>
       <c r="AX23" s="178" t="n">
-        <v>0.9492</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="AY23" s="178" t="n">
-        <v>0.9487</v>
+        <v>0.9179999999999999</v>
       </c>
       <c r="AZ23" s="178" t="n">
-        <v>0.9473</v>
+        <v>0.9149999999999999</v>
       </c>
       <c r="BA23" s="178" t="n">
-        <v>0.9437</v>
+        <v>0.9129999999999999</v>
       </c>
       <c r="BB23" s="178" t="n">
-        <v>0.9417</v>
+        <v>0.9099999999999999</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" thickBot="1">
@@ -4408,16 +4408,16 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>540.5692405659801</v>
+        <v>540.56924056598</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>590.9387062588255</v>
+        <v>590.9387062588254</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>638.0531763714455</v>
+        <v>638.0531763714456</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>683.5994754926787</v>
+        <v>683.5994754926789</v>
       </c>
       <c r="G35" s="150" t="n">
         <v>729.8190325574336</v>
@@ -4426,28 +4426,28 @@
         <v>46.59247602564965</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>53.85657921718551</v>
+        <v>53.85657921718549</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>61.37319407359166</v>
+        <v>61.37319407359168</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>70.13324396302761</v>
+        <v>70.13324396302762</v>
       </c>
       <c r="L35" s="150" t="n">
         <v>80.68027776607101</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>55745531.43349827</v>
+        <v>55745531.43349826</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>65436693.54305295</v>
+        <v>65436693.54305293</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>75593752.53216453</v>
+        <v>75593752.53216454</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>87467017.19417645</v>
+        <v>87467017.19417648</v>
       </c>
       <c r="Q35" s="153" t="n">
         <v>102196467.3450323</v>
@@ -4458,46 +4458,46 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>549.6911181162213</v>
+        <v>549.6911181162212</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>600.9105472621114</v>
+        <v>600.9105472621113</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>648.8200541525582</v>
+        <v>648.8200541525583</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>695.1349278286727</v>
+        <v>695.134927828673</v>
       </c>
       <c r="X35" s="150" t="n">
         <v>742.134420391662</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>56.73791390885657</v>
+        <v>56.73791390885656</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>65.51371983973212</v>
+        <v>65.5137198397321</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>74.57595016109151</v>
+        <v>74.57595016109153</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>85.10289033851427</v>
+        <v>85.1028903385143</v>
       </c>
       <c r="AC35" s="150" t="n">
         <v>97.73368519657591</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>55745531.43349827</v>
+        <v>55745531.43349826</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>65436693.54305295</v>
+        <v>65436693.54305293</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>75593752.53216453</v>
+        <v>75593752.53216454</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>87467017.19417645</v>
+        <v>87467017.19417648</v>
       </c>
       <c r="AH35" s="153" t="n">
         <v>102196467.3450323</v>
@@ -4519,10 +4519,10 @@
         <v>1914.652247498776</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>2045.518265308115</v>
+        <v>2045.518265308116</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>2173.120521689797</v>
+        <v>2173.120521689796</v>
       </c>
       <c r="H36" s="155" t="n">
         <v>105.0017260455107</v>
@@ -4534,10 +4534,10 @@
         <v>131.656194163645</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>149.5920058235545</v>
+        <v>149.5920058235546</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>171.366670105496</v>
+        <v>171.3666701054959</v>
       </c>
       <c r="M36" s="158" t="n">
         <v>27847976.86906923</v>
@@ -4549,10 +4549,10 @@
         <v>35299270.6488976</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>40274580.71405063</v>
+        <v>40274580.71405064</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>46428786.46876455</v>
+        <v>46428786.46876453</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4566,13 +4566,13 @@
         <v>1792.640230577436</v>
       </c>
       <c r="V36" s="156" t="n">
-        <v>1944.755886367749</v>
+        <v>1944.75588636775</v>
       </c>
       <c r="W36" s="156" t="n">
         <v>2077.67948060931</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>2207.287998049624</v>
+        <v>2207.287998049623</v>
       </c>
       <c r="Y36" s="155" t="n">
         <v>105.4473850258541</v>
@@ -4587,7 +4587,7 @@
         <v>150.241110350471</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>172.1221753624089</v>
+        <v>172.1221753624088</v>
       </c>
       <c r="AD36" s="158" t="n">
         <v>27847976.86906923</v>
@@ -4599,10 +4599,10 @@
         <v>35299270.6488976</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>40274580.71405063</v>
+        <v>40274580.71405064</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>46428786.46876455</v>
+        <v>46428786.46876453</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,40 +4612,40 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>694.0250915277974</v>
+        <v>694.0250915277973</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>752.8940651847098</v>
+        <v>752.8940651847097</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>809.9582829507769</v>
+        <v>809.9582829507771</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>865.2243178712292</v>
+        <v>865.2243178712295</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>920.8794661320782</v>
+        <v>920.8794661320779</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>57.19065829931993</v>
+        <v>57.19065829931992</v>
       </c>
       <c r="I37" s="162" t="n">
         <v>65.26892592095186</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>73.93738718357611</v>
+        <v>73.93738718357612</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>84.24090885758746</v>
+        <v>84.24090885758747</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>96.65947346475014</v>
+        <v>96.65947346475012</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>83593508.30256751</v>
+        <v>83593508.3025675</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>96712814.08236293</v>
+        <v>96712814.08236292</v>
       </c>
       <c r="O37" s="165" t="n">
         <v>110893023.1810621</v>
@@ -4662,40 +4662,40 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>705.6213870400774</v>
+        <v>705.6213870400773</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>765.4790825372788</v>
+        <v>765.4790825372787</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>823.5002384213396</v>
+        <v>823.5002384213398</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>879.6915798649409</v>
+        <v>879.6915798649411</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>936.278370594964</v>
+        <v>936.2783705949638</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>67.05704440762081</v>
+        <v>67.05704440762079</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>76.48700151998874</v>
+        <v>76.48700151998872</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>86.59318744033578</v>
+        <v>86.5931874403358</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>98.57776567351952</v>
+        <v>98.57776567351954</v>
       </c>
       <c r="AC37" s="163" t="n">
         <v>112.9881322794499</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>83593508.30256751</v>
+        <v>83593508.3025675</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>96712814.08236293</v>
+        <v>96712814.08236292</v>
       </c>
       <c r="AF37" s="165" t="n">
         <v>110893023.1810621</v>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>1566.667681696046</v>
+        <v>1566.667681696047</v>
       </c>
       <c r="D38" s="156" t="n">
         <v>1724.231054718582</v>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>2062.571309329576</v>
+        <v>2062.571309329577</v>
       </c>
       <c r="U38" s="156" t="n">
         <v>2270.008851058689</v>
@@ -4779,7 +4779,7 @@
         <v>2924.959334771552</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>192.8803621629021</v>
+        <v>192.8803621629022</v>
       </c>
       <c r="Z38" s="156" t="n">
         <v>220.7106826994917</v>
@@ -4822,13 +4822,13 @@
         <v>803.9939146639002</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>865.9524924915833</v>
+        <v>865.9524924915834</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>926.2300002366209</v>
+        <v>926.2300002366211</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>987.0370608328191</v>
+        <v>987.037060832819</v>
       </c>
       <c r="H39" s="161" t="n">
         <v>61.77929571827612</v>
@@ -4840,7 +4840,7 @@
         <v>79.93577187782175</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>91.14560825471899</v>
+        <v>91.14560825471901</v>
       </c>
       <c r="L39" s="163" t="n">
         <v>104.6254293878092</v>
@@ -4875,7 +4875,7 @@
         <v>891.002900874323</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>952.922663427594</v>
+        <v>952.9226634275942</v>
       </c>
       <c r="X39" s="163" t="n">
         <v>1015.301246870969</v>
@@ -4887,7 +4887,7 @@
         <v>82.57469224285403</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>93.55064789392017</v>
+        <v>93.55064789392019</v>
       </c>
       <c r="AB39" s="162" t="n">
         <v>106.5883537949789</v>
@@ -5026,13 +5026,13 @@
         <v>803.9939146639002</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>865.9524924915833</v>
+        <v>865.9524924915834</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>926.2300002366209</v>
+        <v>926.2300002366211</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>987.0370608328191</v>
+        <v>987.037060832819</v>
       </c>
       <c r="H41" s="179" t="n">
         <v>61.77929571827612</v>
@@ -5044,7 +5044,7 @@
         <v>79.93577187782175</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>91.14560825471899</v>
+        <v>91.14560825471901</v>
       </c>
       <c r="L41" s="181" t="n">
         <v>104.6254293878092</v>
@@ -5079,7 +5079,7 @@
         <v>891.002900874323</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>952.922663427594</v>
+        <v>952.9226634275942</v>
       </c>
       <c r="X41" s="187" t="n">
         <v>1015.301246870969</v>
@@ -5091,7 +5091,7 @@
         <v>82.57469224285403</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>93.55064789392017</v>
+        <v>93.55064789392019</v>
       </c>
       <c r="AB41" s="186" t="n">
         <v>106.5883537949789</v>
@@ -5424,7 +5424,7 @@
         <v>0.184986997180821</v>
       </c>
       <c r="U46" s="149" t="n">
-        <v>0.205162078248975</v>
+        <v>0.2051620782489751</v>
       </c>
       <c r="V46" s="149" t="n">
         <v>0.2290310661563521</v>
@@ -5479,7 +5479,7 @@
         <v>0.04143667480756179</v>
       </c>
       <c r="E47" s="156" t="n">
-        <v>0.041874974291546</v>
+        <v>0.04187497429154601</v>
       </c>
       <c r="F47" s="156" t="n">
         <v>0.04117045304614886</v>
@@ -5529,7 +5529,7 @@
         <v>0.04208817415736146</v>
       </c>
       <c r="V47" s="156" t="n">
-        <v>0.04253336492377023</v>
+        <v>0.04253336492377024</v>
       </c>
       <c r="W47" s="156" t="n">
         <v>0.04181776665215348</v>
@@ -5578,7 +5578,7 @@
         <v>0.1615583391258168</v>
       </c>
       <c r="D48" s="162" t="n">
-        <v>0.1796400717568938</v>
+        <v>0.1796400717568939</v>
       </c>
       <c r="E48" s="162" t="n">
         <v>0.200540004602406</v>
@@ -5593,7 +5593,7 @@
         <v>0.01331310334617804</v>
       </c>
       <c r="I48" s="162" t="n">
-        <v>0.01557312652352847</v>
+        <v>0.01557312652352848</v>
       </c>
       <c r="J48" s="162" t="n">
         <v>0.01830637982003985</v>
@@ -5608,7 +5608,7 @@
         <v>19459.27968300562</v>
       </c>
       <c r="N48" s="165" t="n">
-        <v>23075.61935330771</v>
+        <v>23075.61935330772</v>
       </c>
       <c r="O48" s="165" t="n">
         <v>27456.3367610581</v>
@@ -5658,7 +5658,7 @@
         <v>19459.27968300562</v>
       </c>
       <c r="AE48" s="165" t="n">
-        <v>23075.61935330771</v>
+        <v>23075.61935330772</v>
       </c>
       <c r="AF48" s="165" t="n">
         <v>27456.3367610581</v>
@@ -5689,7 +5689,7 @@
         <v>0.2265826015246185</v>
       </c>
       <c r="G49" s="157" t="n">
-        <v>0.2352242498407841</v>
+        <v>0.235224249840784</v>
       </c>
       <c r="H49" s="155" t="n">
         <v>0.02135684474722451</v>
@@ -5704,7 +5704,7 @@
         <v>0.0277508639872541</v>
       </c>
       <c r="L49" s="157" t="n">
-        <v>0.03055805771288122</v>
+        <v>0.03055805771288121</v>
       </c>
       <c r="M49" s="158" t="n">
         <v>1351.390929613833</v>
@@ -5733,13 +5733,13 @@
         <v>0.2738368786746762</v>
       </c>
       <c r="V49" s="156" t="n">
-        <v>0.2868456480863866</v>
+        <v>0.2868456480863867</v>
       </c>
       <c r="W49" s="156" t="n">
         <v>0.2983037044537724</v>
       </c>
       <c r="X49" s="157" t="n">
-        <v>0.3096807284968951</v>
+        <v>0.309680728496895</v>
       </c>
       <c r="Y49" s="155" t="n">
         <v>0.02455265558621287</v>
@@ -5812,7 +5812,7 @@
         <v>20810.67061261945</v>
       </c>
       <c r="N50" s="165" t="n">
-        <v>24559.26387879241</v>
+        <v>24559.26387879242</v>
       </c>
       <c r="O50" s="165" t="n">
         <v>29096.03938828722</v>
@@ -5847,7 +5847,7 @@
         <v>0.01598799621339435</v>
       </c>
       <c r="Z50" s="162" t="n">
-        <v>0.01860326748902334</v>
+        <v>0.01860326748902335</v>
       </c>
       <c r="AA50" s="162" t="n">
         <v>0.0217623547329069</v>
@@ -5862,7 +5862,7 @@
         <v>20810.67061261945</v>
       </c>
       <c r="AE50" s="165" t="n">
-        <v>24559.26387879241</v>
+        <v>24559.26387879242</v>
       </c>
       <c r="AF50" s="165" t="n">
         <v>29096.03938828722</v>
@@ -6016,7 +6016,7 @@
         <v>20810.67061261945</v>
       </c>
       <c r="N52" s="183" t="n">
-        <v>24559.26387879241</v>
+        <v>24559.26387879242</v>
       </c>
       <c r="O52" s="183" t="n">
         <v>29096.03938828722</v>
@@ -6051,7 +6051,7 @@
         <v>0.01598799621339435</v>
       </c>
       <c r="Z52" s="186" t="n">
-        <v>0.01860326748902334</v>
+        <v>0.01860326748902335</v>
       </c>
       <c r="AA52" s="186" t="n">
         <v>0.0217623547329069</v>
@@ -6066,7 +6066,7 @@
         <v>20810.67061261945</v>
       </c>
       <c r="AE52" s="189" t="n">
-        <v>24559.26387879241</v>
+        <v>24559.26387879242</v>
       </c>
       <c r="AF52" s="189" t="n">
         <v>29096.03938828722</v>
@@ -6337,10 +6337,10 @@
         <v>0.01034250027988828</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.009529046918664089</v>
+        <v>0.00952904691866409</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.008814070349602297</v>
+        <v>0.008814070349602292</v>
       </c>
       <c r="F57" s="149" t="n">
         <v>0.000320639402826937</v>
@@ -6352,10 +6352,10 @@
         <v>0.0008914356574033601</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.0008684519473911942</v>
+        <v>0.0008684519473911944</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.0008478096656782673</v>
+        <v>0.0008478096656782668</v>
       </c>
       <c r="K57" s="149" t="n">
         <v>3.289569736198823e-05</v>
@@ -6370,7 +6370,7 @@
         <v>1055.184431768946</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>1044.252544275467</v>
+        <v>1044.252544275466</v>
       </c>
       <c r="P57" s="152" t="n">
         <v>41.02602937192354</v>
@@ -6387,10 +6387,10 @@
         <v>0.01051702560252354</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.009689845559503417</v>
+        <v>0.009689845559503418</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.008962804062908116</v>
+        <v>0.008962804062908109</v>
       </c>
       <c r="W57" s="149" t="n">
         <v>0.0003260500572831681</v>
@@ -6405,7 +6405,7 @@
         <v>0.001056426501694732</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.001030192616305753</v>
+        <v>0.001030192616305752</v>
       </c>
       <c r="AB57" s="149" t="n">
         <v>3.991714580723046e-05</v>
@@ -6420,7 +6420,7 @@
         <v>1055.184431768946</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>1044.252544275467</v>
+        <v>1044.252544275466</v>
       </c>
       <c r="AG57" s="152" t="n">
         <v>41.02602937192354</v>
@@ -6541,10 +6541,10 @@
         <v>0.008854965861558158</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.008214445044247953</v>
+        <v>0.008214445044247955</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.007627179541740365</v>
+        <v>0.00762717954174036</v>
       </c>
       <c r="F59" s="162" t="n">
         <v>0.0002778790844920332</v>
@@ -6556,10 +6556,10 @@
         <v>0.0007296873456342929</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.0007121161261155844</v>
+        <v>0.0007121161261155845</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.0006962503363035298</v>
+        <v>0.0006962503363035292</v>
       </c>
       <c r="K59" s="162" t="n">
         <v>2.705516494002093e-05</v>
@@ -6574,7 +6574,7 @@
         <v>1055.184431768946</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>1044.252544275467</v>
+        <v>1044.252544275466</v>
       </c>
       <c r="P59" s="165" t="n">
         <v>41.02602937192354</v>
@@ -6591,10 +6591,10 @@
         <v>0.009002921320424542</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.008351753781564435</v>
+        <v>0.008351753781564436</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.007754700832520858</v>
+        <v>0.007754700832520852</v>
       </c>
       <c r="W59" s="162" t="n">
         <v>0.0002825254512606072</v>
@@ -6606,10 +6606,10 @@
         <v>0.0008555711403738043</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.000834510855695369</v>
+        <v>0.0008345108556953692</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.0008154269196345208</v>
+        <v>0.0008154269196345204</v>
       </c>
       <c r="AB59" s="162" t="n">
         <v>3.165965023269794e-05</v>
@@ -6624,7 +6624,7 @@
         <v>1055.184431768946</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>1044.252544275467</v>
+        <v>1044.252544275466</v>
       </c>
       <c r="AG59" s="165" t="n">
         <v>41.02602937192354</v>
@@ -6745,10 +6745,10 @@
         <v>0.008383323812720587</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.007782301607069076</v>
+        <v>0.007782301607069077</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.007229775608787332</v>
+        <v>0.007229775608787327</v>
       </c>
       <c r="F61" s="162" t="n">
         <v>0.0002635306532242604</v>
@@ -6760,10 +6760,10 @@
         <v>0.0006994092989374289</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.0006825875452042293</v>
+        <v>0.0006825875452042294</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.0006673780591924113</v>
+        <v>0.0006673780591924109</v>
       </c>
       <c r="K61" s="162" t="n">
         <v>2.59327183051212e-05</v>
@@ -6778,7 +6778,7 @@
         <v>1055.184431768946</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>1044.252544275467</v>
+        <v>1044.252544275466</v>
       </c>
       <c r="P61" s="165" t="n">
         <v>41.02602937192354</v>
@@ -6795,10 +6795,10 @@
         <v>0.008628057288799409</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.008008330891146956</v>
+        <v>0.008008330891146958</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.007438919682031573</v>
+        <v>0.007438919682031569</v>
       </c>
       <c r="W61" s="162" t="n">
         <v>0.0002711252409240922</v>
@@ -6810,10 +6810,10 @@
         <v>0.0008193929686340282</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.0007992860995887476</v>
+        <v>0.0007992860995887478</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.0007810476881747527</v>
+        <v>0.0007810476881747522</v>
       </c>
       <c r="AB61" s="162" t="n">
         <v>3.03264831570058e-05</v>
@@ -6828,7 +6828,7 @@
         <v>1055.184431768946</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>1044.252544275467</v>
+        <v>1044.252544275466</v>
       </c>
       <c r="AG61" s="165" t="n">
         <v>41.02602937192354</v>
@@ -6949,10 +6949,10 @@
         <v>0.008383323812720587</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.007782301607069076</v>
+        <v>0.007782301607069077</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.007229775608787332</v>
+        <v>0.007229775608787327</v>
       </c>
       <c r="F63" s="180" t="n">
         <v>0.0002635306532242604</v>
@@ -6964,10 +6964,10 @@
         <v>0.0006994092989374289</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.0006825875452042293</v>
+        <v>0.0006825875452042294</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.0006673780591924113</v>
+        <v>0.0006673780591924109</v>
       </c>
       <c r="K63" s="180" t="n">
         <v>2.59327183051212e-05</v>
@@ -6982,7 +6982,7 @@
         <v>1055.184431768946</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>1044.252544275467</v>
+        <v>1044.252544275466</v>
       </c>
       <c r="P63" s="183" t="n">
         <v>41.02602937192354</v>
@@ -6999,10 +6999,10 @@
         <v>0.008628057288799409</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.008008330891146956</v>
+        <v>0.008008330891146958</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.007438919682031573</v>
+        <v>0.007438919682031569</v>
       </c>
       <c r="W63" s="186" t="n">
         <v>0.0002711252409240922</v>
@@ -7014,10 +7014,10 @@
         <v>0.0008193929686340282</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.0007992860995887476</v>
+        <v>0.0007992860995887478</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.0007810476881747527</v>
+        <v>0.0007810476881747522</v>
       </c>
       <c r="AB63" s="186" t="n">
         <v>3.03264831570058e-05</v>
@@ -7032,7 +7032,7 @@
         <v>1055.184431768946</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>1044.252544275467</v>
+        <v>1044.252544275466</v>
       </c>
       <c r="AG63" s="189" t="n">
         <v>41.02602937192354</v>
@@ -7300,10 +7300,10 @@
         <v>0.004389790632988982</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.006387224154446729</v>
+        <v>0.006387224154446731</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.008442347676483802</v>
+        <v>0.008442347676483795</v>
       </c>
       <c r="F68" s="149" t="n">
         <v>0.01031668646141137</v>
@@ -7315,10 +7315,10 @@
         <v>0.0003783626582434007</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.0005821145915955873</v>
+        <v>0.0005821145915955875</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.000812054326462505</v>
+        <v>0.0008120543264625044</v>
       </c>
       <c r="K68" s="149" t="n">
         <v>0.001058430725048115</v>
@@ -7330,10 +7330,10 @@
         <v>452.691705990428</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>707.2794947404479</v>
+        <v>707.2794947404482</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>1000.212466108133</v>
+        <v>1000.212466108132</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>1320.027039893274</v>
@@ -7350,25 +7350,25 @@
         <v>0.004463866495284432</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.006495005863524004</v>
+        <v>0.006495005863524007</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.008584808726729315</v>
+        <v>0.008584808726729308</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.01049077618676588</v>
+        <v>0.01049077618676587</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.01225002419731908</v>
+        <v>0.01225002419731909</v>
       </c>
       <c r="Y68" s="148" t="n">
         <v>0.000460750528002034</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.0007081120416991528</v>
+        <v>0.0007081120416991531</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.0009867454984622483</v>
+        <v>0.0009867454984622476</v>
       </c>
       <c r="AB68" s="149" t="n">
         <v>0.001284348318069664</v>
@@ -7380,10 +7380,10 @@
         <v>452.691705990428</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>707.2794947404479</v>
+        <v>707.2794947404482</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>1000.212466108133</v>
+        <v>1000.212466108132</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>1320.027039893274</v>
@@ -7504,40 +7504,40 @@
         <v>0.003758418674650023</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.005506059761257988</v>
+        <v>0.00550605976125799</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.007305512541687619</v>
+        <v>0.007305512541687613</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.008940858059281243</v>
+        <v>0.008940858059281241</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.01045202489141598</v>
+        <v>0.01045202489141599</v>
       </c>
       <c r="H70" s="161" t="n">
         <v>0.0003097098949182347</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.0004773242655136551</v>
+        <v>0.0004773242655136552</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.0006668868270615054</v>
+        <v>0.000666886827061505</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.000870509523742528</v>
+        <v>0.0008705095237425278</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.001097089532127573</v>
+        <v>0.001097089532127574</v>
       </c>
       <c r="M70" s="164" t="n">
         <v>452.691705990428</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>707.2794947404479</v>
+        <v>707.2794947404482</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>1000.212466108133</v>
+        <v>1000.212466108132</v>
       </c>
       <c r="P70" s="165" t="n">
         <v>1320.027039893274</v>
@@ -7554,13 +7554,13 @@
         <v>0.003821217173064786</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.005598096424639992</v>
+        <v>0.005598096424639994</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.007427655777471015</v>
+        <v>0.007427655777471009</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.009090356557324453</v>
+        <v>0.009090356557324451</v>
       </c>
       <c r="X70" s="163" t="n">
         <v>0.01062680317529134</v>
@@ -7569,10 +7569,10 @@
         <v>0.0003631402539260263</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.0005593642197527065</v>
+        <v>0.0005593642197527066</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.0007810372832603342</v>
+        <v>0.0007810372832603335</v>
       </c>
       <c r="AB70" s="162" t="n">
         <v>0.001018660470450622</v>
@@ -7584,10 +7584,10 @@
         <v>452.691705990428</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>707.2794947404479</v>
+        <v>707.2794947404482</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>1000.212466108133</v>
+        <v>1000.212466108132</v>
       </c>
       <c r="AG70" s="165" t="n">
         <v>1320.027039893274</v>
@@ -7615,7 +7615,7 @@
         <v>0.02891214347838031</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.03493993914006311</v>
+        <v>0.0349399391400631</v>
       </c>
       <c r="H71" s="155" t="n">
         <v>0.001202013507294912</v>
@@ -7630,7 +7630,7 @@
         <v>0.003541035171499399</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.004539058695901023</v>
+        <v>0.004539058695901022</v>
       </c>
       <c r="M71" s="158" t="n">
         <v>76.05946338317402</v>
@@ -7642,10 +7642,10 @@
         <v>172.5671234889683</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>232.4112790862741</v>
+        <v>232.411279086274</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>302.1614577989031</v>
+        <v>302.161457798903</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>0.03806382063436034</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.04599961872067099</v>
+        <v>0.04599961872067098</v>
       </c>
       <c r="Y71" s="155" t="n">
         <v>0.001381881265884238</v>
@@ -7680,7 +7680,7 @@
         <v>0.004079822765281677</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.005235238901192118</v>
+        <v>0.005235238901192117</v>
       </c>
       <c r="AD71" s="158" t="n">
         <v>76.05946338317402</v>
@@ -7692,10 +7692,10 @@
         <v>172.5671234889683</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>232.4112790862741</v>
+        <v>232.411279086274</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>302.1614577989031</v>
+        <v>302.161457798903</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7708,13 +7708,13 @@
         <v>0.004156074374709214</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.00610363474363278</v>
+        <v>0.006103634743632782</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.008119619452050914</v>
+        <v>0.008119619452050909</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.009972085784422362</v>
+        <v>0.009972085784422361</v>
       </c>
       <c r="G72" s="163" t="n">
         <v>0.01169742855839941</v>
@@ -7723,13 +7723,13 @@
         <v>0.0003467356301251902</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.0005353512709781264</v>
+        <v>0.0005353512709781266</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.0007495192333084882</v>
+        <v>0.0007495192333084878</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.000981302510345396</v>
+        <v>0.0009813025103453958</v>
       </c>
       <c r="L72" s="163" t="n">
         <v>0.001239921512798243</v>
@@ -7738,10 +7738,10 @@
         <v>528.751169373602</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>827.5778405754851</v>
+        <v>827.5778405754853</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>1172.779589597101</v>
+        <v>1172.7795895971</v>
       </c>
       <c r="P72" s="165" t="n">
         <v>1552.438318979548</v>
@@ -7758,13 +7758,13 @@
         <v>0.00427740220974063</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.006280908802263846</v>
+        <v>0.006280908802263848</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.008354505066388804</v>
+        <v>0.008354505066388799</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>0.01025946745753496</v>
+        <v>0.01025946745753495</v>
       </c>
       <c r="X72" s="163" t="n">
         <v>0.01203238892621337</v>
@@ -7773,10 +7773,10 @@
         <v>0.0004062181296861589</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.0006268775811928397</v>
+        <v>0.0006268775811928398</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.0008771793683575812</v>
+        <v>0.0008771793683575807</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.001147564003964839</v>
@@ -7788,10 +7788,10 @@
         <v>528.751169373602</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>827.5778405754851</v>
+        <v>827.5778405754853</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>1172.779589597101</v>
+        <v>1172.7795895971</v>
       </c>
       <c r="AG72" s="165" t="n">
         <v>1552.438318979548</v>
@@ -7912,13 +7912,13 @@
         <v>0.004156074374709214</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.00610363474363278</v>
+        <v>0.006103634743632782</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.008119619452050914</v>
+        <v>0.008119619452050909</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.009972085784422362</v>
+        <v>0.009972085784422361</v>
       </c>
       <c r="G74" s="181" t="n">
         <v>0.01169742855839941</v>
@@ -7927,13 +7927,13 @@
         <v>0.0003467356301251902</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.0005353512709781264</v>
+        <v>0.0005353512709781266</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.0007495192333084882</v>
+        <v>0.0007495192333084878</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.000981302510345396</v>
+        <v>0.0009813025103453958</v>
       </c>
       <c r="L74" s="181" t="n">
         <v>0.001239921512798243</v>
@@ -7942,10 +7942,10 @@
         <v>528.751169373602</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>827.5778405754851</v>
+        <v>827.5778405754853</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>1172.779589597101</v>
+        <v>1172.7795895971</v>
       </c>
       <c r="P74" s="183" t="n">
         <v>1552.438318979548</v>
@@ -7962,13 +7962,13 @@
         <v>0.00427740220974063</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.006280908802263846</v>
+        <v>0.006280908802263848</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.008354505066388804</v>
+        <v>0.008354505066388799</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.01025946745753496</v>
+        <v>0.01025946745753495</v>
       </c>
       <c r="X74" s="187" t="n">
         <v>0.01203238892621337</v>
@@ -7977,10 +7977,10 @@
         <v>0.0004062181296861589</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.0006268775811928397</v>
+        <v>0.0006268775811928398</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.0008771793683575812</v>
+        <v>0.0008771793683575807</v>
       </c>
       <c r="AB74" s="186" t="n">
         <v>0.001147564003964839</v>
@@ -7992,10 +7992,10 @@
         <v>528.751169373602</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>827.5778405754851</v>
+        <v>827.5778405754853</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>1172.779589597101</v>
+        <v>1172.7795895971</v>
       </c>
       <c r="AG74" s="189" t="n">
         <v>1552.438318979548</v>
@@ -8260,46 +8260,46 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>540.7658900778284</v>
+        <v>540.7658900778283</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>591.1563800354811</v>
+        <v>591.156380035481</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>638.2956631878131</v>
+        <v>638.2956631878133</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>683.8594162227295</v>
+        <v>683.8594162227297</v>
       </c>
       <c r="G79" s="150" t="n">
         <v>730.1040237956695</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>46.6094255428968</v>
+        <v>46.60942554289679</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>53.87641742522941</v>
+        <v>53.87641742522939</v>
       </c>
       <c r="J79" s="149" t="n">
         <v>61.39651844684509</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>70.15991233725863</v>
+        <v>70.15991233725866</v>
       </c>
       <c r="L79" s="150" t="n">
         <v>80.71178307250459</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>55765810.67012788</v>
+        <v>55765810.67012787</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>65460797.31568539</v>
+        <v>65460797.31568538</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>75622481.31068586</v>
+        <v>75622481.31068587</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>87500276.78713976</v>
+        <v>87500276.78713979</v>
       </c>
       <c r="Q79" s="153" t="n">
         <v>102236374.6322812</v>
@@ -8310,16 +8310,16 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>549.8910860054999</v>
+        <v>549.8910860054998</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>601.1318941917834</v>
+        <v>601.1318941917833</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>649.0666328315041</v>
+        <v>649.0666328315042</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>695.3992549487211</v>
+        <v>695.3992549487214</v>
       </c>
       <c r="X79" s="150" t="n">
         <v>742.4242207366377</v>
@@ -8328,28 +8328,28 @@
         <v>56.75855415664756</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>65.53785198519701</v>
+        <v>65.53785198519699</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>74.60429213226544</v>
+        <v>74.60429213226546</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>85.13525096522201</v>
+        <v>85.13525096522204</v>
       </c>
       <c r="AC79" s="150" t="n">
         <v>97.77184978631527</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>55765810.67012788</v>
+        <v>55765810.67012787</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>65460797.31568539</v>
+        <v>65460797.31568538</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>75622481.31068586</v>
+        <v>75622481.31068587</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>87500276.78713976</v>
+        <v>87500276.78713979</v>
       </c>
       <c r="AH79" s="153" t="n">
         <v>102236374.6322812</v>
@@ -8368,13 +8368,13 @@
         <v>1764.932686261068</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>1914.694122473067</v>
+        <v>1914.694122473068</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>2045.559435761161</v>
+        <v>2045.559435761162</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>2173.160257120019</v>
+        <v>2173.160257120018</v>
       </c>
       <c r="H80" s="155" t="n">
         <v>105.0043627502862</v>
@@ -8389,7 +8389,7 @@
         <v>149.5950166843013</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>171.3698035388672</v>
+        <v>171.3698035388671</v>
       </c>
       <c r="M80" s="158" t="n">
         <v>27848676.16132244</v>
@@ -8401,10 +8401,10 @@
         <v>35300042.67214771</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>40275391.32657967</v>
+        <v>40275391.32657968</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>46429635.41744762</v>
+        <v>46429635.4174476</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8421,10 +8421,10 @@
         <v>1944.798419732673</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>2077.721298375962</v>
+        <v>2077.721298375963</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>2207.328358230917</v>
+        <v>2207.328358230916</v>
       </c>
       <c r="Y80" s="155" t="n">
         <v>105.4500329215995</v>
@@ -8451,10 +8451,10 @@
         <v>35300042.67214771</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>40275391.32657967</v>
+        <v>40275391.32657968</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>46429635.41744762</v>
+        <v>46429635.4174476</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8467,16 +8467,16 @@
         <v>694.1992632514593</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>753.0874257612722</v>
+        <v>753.0874257612721</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>810.1737556474627</v>
+        <v>810.1737556474628</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>865.455083501138</v>
+        <v>865.4550835011382</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>921.131991055155</v>
+        <v>921.1319910551548</v>
       </c>
       <c r="H81" s="161" t="n">
         <v>57.20501079990665</v>
@@ -8485,25 +8485,25 @@
         <v>65.28568848786702</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>73.95705670055951</v>
+        <v>73.95705670055952</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>84.26337691124138</v>
+        <v>84.26337691124139</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>96.68597956788203</v>
+        <v>96.685979567882</v>
       </c>
       <c r="M81" s="164" t="n">
         <v>83614486.83145031</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>96737652.16564275</v>
+        <v>96737652.16564274</v>
       </c>
       <c r="O81" s="165" t="n">
         <v>110922523.9828336</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>127775668.1137194</v>
+        <v>127775668.1137195</v>
       </c>
       <c r="Q81" s="166" t="n">
         <v>148666010.0497288</v>
@@ -8517,43 +8517,43 @@
         <v>705.7984689564718</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>765.6756752368236</v>
+        <v>765.6756752368235</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>823.7193136759905</v>
+        <v>823.7193136759906</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>879.9262040859203</v>
+        <v>879.9262040859205</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>936.5351182282956</v>
+        <v>936.5351182282953</v>
       </c>
       <c r="Y81" s="161" t="n">
         <v>67.07387296490313</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>76.50664514768795</v>
+        <v>76.50664514768793</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>86.61622377196561</v>
+        <v>86.61622377196562</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>98.60405753763011</v>
+        <v>98.60405753763014</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>113.0191160514438</v>
+        <v>113.0191160514437</v>
       </c>
       <c r="AD81" s="164" t="n">
         <v>83614486.83145031</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>96737652.16564275</v>
+        <v>96737652.16564274</v>
       </c>
       <c r="AF81" s="165" t="n">
         <v>110922523.9828336</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>127775668.1137194</v>
+        <v>127775668.1137195</v>
       </c>
       <c r="AH81" s="166" t="n">
         <v>148666010.0497288</v>
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>2062.848640992748</v>
+        <v>2062.848640992749</v>
       </c>
       <c r="U82" s="156" t="n">
         <v>2270.304891452402</v>
@@ -8631,7 +8631,7 @@
         <v>2925.315015118769</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>192.9062966997542</v>
+        <v>192.9062966997543</v>
       </c>
       <c r="Z82" s="156" t="n">
         <v>220.7394664099043</v>
@@ -8671,28 +8671,28 @@
         <v>740.6807688387987</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>804.1889325360511</v>
+        <v>804.188932536051</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>866.1692853373063</v>
+        <v>866.1692853373065</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>926.4620427672681</v>
+        <v>926.4620427672685</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>987.2904828517537</v>
+        <v>987.2904828517536</v>
       </c>
       <c r="H83" s="161" t="n">
         <v>61.79398873796622</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>70.53560463932305</v>
+        <v>70.53560463932304</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>79.9557839496279</v>
+        <v>79.95578394962791</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>91.16844238618893</v>
+        <v>91.16844238618897</v>
       </c>
       <c r="L83" s="163" t="n">
         <v>104.6522919936824</v>
@@ -8704,10 +8704,10 @@
         <v>109038133.5313617</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>125107545.3693726</v>
+        <v>125107545.3693727</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>144230124.7065825</v>
+        <v>144230124.7065826</v>
       </c>
       <c r="Q83" s="166" t="n">
         <v>167881766.0510302</v>
@@ -8721,13 +8721,13 @@
         <v>762.3033833616448</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>827.5458079004507</v>
+        <v>827.5458079004505</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>891.2259651372045</v>
+        <v>891.2259651372046</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>953.1613931019474</v>
+        <v>953.1613931019479</v>
       </c>
       <c r="X83" s="163" t="n">
         <v>1015.56192572693</v>
@@ -8736,16 +8736,16 @@
         <v>72.39474790035594</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>82.59472167402384</v>
+        <v>82.59472167402383</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>93.57406847570959</v>
+        <v>93.57406847570962</v>
       </c>
       <c r="AB83" s="162" t="n">
         <v>106.6150566995985</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>122.262754135216</v>
+        <v>122.2627541352159</v>
       </c>
       <c r="AD83" s="164" t="n">
         <v>94232149.70339765</v>
@@ -8754,10 +8754,10 @@
         <v>109038133.5313617</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>125107545.3693726</v>
+        <v>125107545.3693727</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>144230124.7065825</v>
+        <v>144230124.7065826</v>
       </c>
       <c r="AH83" s="166" t="n">
         <v>167881766.0510302</v>
@@ -8875,28 +8875,28 @@
         <v>740.6807688387987</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>804.1889325360511</v>
+        <v>804.188932536051</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>866.1692853373063</v>
+        <v>866.1692853373065</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>926.4620427672681</v>
+        <v>926.4620427672685</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>987.2904828517537</v>
+        <v>987.2904828517536</v>
       </c>
       <c r="H85" s="179" t="n">
         <v>61.79398873796622</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>70.53560463932305</v>
+        <v>70.53560463932304</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>79.9557839496279</v>
+        <v>79.95578394962791</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>91.16844238618893</v>
+        <v>91.16844238618897</v>
       </c>
       <c r="L85" s="181" t="n">
         <v>104.6522919936824</v>
@@ -8908,10 +8908,10 @@
         <v>109038133.5313617</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>125107545.3693726</v>
+        <v>125107545.3693727</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>144230124.7065825</v>
+        <v>144230124.7065826</v>
       </c>
       <c r="Q85" s="184" t="n">
         <v>167881766.0510302</v>
@@ -8925,13 +8925,13 @@
         <v>762.3033833616448</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>827.5458079004507</v>
+        <v>827.5458079004505</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>891.2259651372045</v>
+        <v>891.2259651372046</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>953.1613931019474</v>
+        <v>953.1613931019479</v>
       </c>
       <c r="X85" s="187" t="n">
         <v>1015.56192572693</v>
@@ -8940,16 +8940,16 @@
         <v>72.39474790035594</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>82.59472167402384</v>
+        <v>82.59472167402383</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>93.57406847570959</v>
+        <v>93.57406847570962</v>
       </c>
       <c r="AB85" s="186" t="n">
         <v>106.6150566995985</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>122.262754135216</v>
+        <v>122.2627541352159</v>
       </c>
       <c r="AD85" s="188" t="n">
         <v>94232149.70339765</v>
@@ -8958,10 +8958,10 @@
         <v>109038133.5313617</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>125107545.3693726</v>
+        <v>125107545.3693727</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>144230124.7065825</v>
+        <v>144230124.7065826</v>
       </c>
       <c r="AH85" s="190" t="n">
         <v>167881766.0510302</v>
@@ -9410,7 +9410,7 @@
         <v>17721.2735043261</v>
       </c>
       <c r="E91" s="80" t="n">
-        <v>18436.38744059719</v>
+        <v>18436.38744059718</v>
       </c>
       <c r="F91" s="80" t="n">
         <v>19689.18165978053</v>
